--- a/analysis/corrected_working/SF_18O_18F.xlsx
+++ b/analysis/corrected_working/SF_18O_18F.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kawecka/digios/analysis/corrected_working/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E65D4D1-3ADD-3D47-A075-F2B2DF7B72EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888F6C3F-4D93-9F45-B70E-1A7FEB94C52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17220" xr2:uid="{3ABE6ABB-8332-1E45-BF21-9E3D8711C9F0}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="29">
   <si>
     <t>1,982 MeV</t>
   </si>
@@ -104,6 +104,27 @@
   <si>
     <t>3.920 MeV</t>
   </si>
+  <si>
+    <t xml:space="preserve"> 0dX/2//1s1/2</t>
+  </si>
+  <si>
+    <t>diff</t>
+  </si>
+  <si>
+    <t>3.553 MeV</t>
+  </si>
+  <si>
+    <t>3.552</t>
+  </si>
+  <si>
+    <t>3.630</t>
+  </si>
+  <si>
+    <t>5.255 MeV</t>
+  </si>
+  <si>
+    <t>0 MeV (gs)</t>
+  </si>
 </sst>
 </file>
 
@@ -125,7 +146,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -138,8 +159,80 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -190,17 +283,102 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -535,17 +713,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC19792A-629E-104B-BC7C-CEC29C61C0D2}">
-  <dimension ref="B1:J39"/>
+  <dimension ref="B1:S39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="4.1640625" customWidth="1"/>
     <col min="3" max="3" width="3.33203125" customWidth="1"/>
     <col min="6" max="6" width="11.6640625" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:19" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D2" s="5" t="s">
         <v>0</v>
       </c>
@@ -553,19 +731,28 @@
         <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="2:19" x14ac:dyDescent="0.2">
       <c r="D3" t="s">
         <v>18</v>
       </c>
@@ -573,12 +760,18 @@
         <f>0.83/0.21</f>
         <v>3.9523809523809526</v>
       </c>
-      <c r="J3" s="3">
+      <c r="K3" s="3">
         <f>0.66/0.35</f>
         <v>1.8857142857142859</v>
       </c>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19" x14ac:dyDescent="0.2">
       <c r="D4" s="4" t="s">
         <v>1</v>
       </c>
@@ -588,21 +781,40 @@
       <c r="F4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="G4" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="35"/>
+      <c r="I4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
+      <c r="L4" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="30" t="s">
         <v>5</v>
       </c>
       <c r="D5">
@@ -611,16 +823,46 @@
       <c r="E5">
         <v>3.0304000000000002</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="6">
         <f>E5/D5</f>
         <v>5.9448282897240627</v>
       </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
+      <c r="G5">
+        <f>ABS(F5-$F$3)</f>
+        <v>1.9924473373431102</v>
+      </c>
+      <c r="I5">
+        <v>1.2305999999999999</v>
+      </c>
+      <c r="J5">
+        <v>1.80183</v>
+      </c>
+      <c r="K5" s="6">
+        <f>J5/I5</f>
+        <v>1.4641882008776208</v>
+      </c>
+      <c r="L5">
+        <f>ABS(K5-$K$3)</f>
+        <v>0.42152608483666509</v>
+      </c>
+      <c r="N5">
+        <v>5.51715</v>
+      </c>
+      <c r="O5">
+        <v>48.037199999999999</v>
+      </c>
+      <c r="Q5">
+        <v>7.0998700000000001</v>
+      </c>
+      <c r="S5">
+        <v>3.2964500000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="31" t="s">
         <v>6</v>
       </c>
       <c r="D6">
@@ -629,16 +871,46 @@
       <c r="E6">
         <v>3.1882600000000001</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="7">
         <f t="shared" ref="F6:F39" si="0">E6/D6</f>
         <v>6.1273689247805727</v>
       </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
+      <c r="G6">
+        <f t="shared" ref="G6:G39" si="1">ABS(F6-$F$3)</f>
+        <v>2.1749879723996202</v>
+      </c>
+      <c r="I6">
+        <v>1.2332799999999999</v>
+      </c>
+      <c r="J6">
+        <v>1.8972</v>
+      </c>
+      <c r="K6" s="7">
+        <f>J6/I6</f>
+        <v>1.5383367929423977</v>
+      </c>
+      <c r="L6">
+        <f>ABS(K6-$K$3)</f>
+        <v>0.34737749277188823</v>
+      </c>
+      <c r="N6">
+        <v>5.5908699999999998</v>
+      </c>
+      <c r="O6">
+        <v>49.734999999999999</v>
+      </c>
+      <c r="Q6">
+        <v>7.7332799999999997</v>
+      </c>
+      <c r="S6">
+        <v>3.4656600000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D7">
@@ -647,16 +919,46 @@
       <c r="E7">
         <v>3.51823</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="7">
         <f t="shared" si="0"/>
         <v>6.9105362091960298</v>
       </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
+      <c r="G7">
+        <f t="shared" si="1"/>
+        <v>2.9581552568150773</v>
+      </c>
+      <c r="I7">
+        <v>1.2446200000000001</v>
+      </c>
+      <c r="J7">
+        <v>2.1539899999999998</v>
+      </c>
+      <c r="K7" s="7">
+        <f t="shared" ref="K7:K23" si="2">J7/I7</f>
+        <v>1.7306406774758558</v>
+      </c>
+      <c r="L7">
+        <f>ABS(K7-$K$3)</f>
+        <v>0.15507360823843008</v>
+      </c>
+      <c r="N7">
+        <v>6.2110300000000001</v>
+      </c>
+      <c r="O7">
+        <v>55.26</v>
+      </c>
+      <c r="Q7">
+        <v>7.6856</v>
+      </c>
+      <c r="S7">
+        <v>3.7284000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B8" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="33" t="s">
         <v>8</v>
       </c>
       <c r="D8">
@@ -665,16 +967,46 @@
       <c r="E8">
         <v>3.3570099999999998</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="7">
         <f t="shared" si="0"/>
         <v>6.4035869136023829</v>
       </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
+      <c r="G8">
+        <f t="shared" si="1"/>
+        <v>2.4512059612214303</v>
+      </c>
+      <c r="I8">
+        <v>1.26976</v>
+      </c>
+      <c r="J8">
+        <v>1.9996700000000001</v>
+      </c>
+      <c r="K8" s="7">
+        <f t="shared" si="2"/>
+        <v>1.5748409148185485</v>
+      </c>
+      <c r="L8">
+        <f>ABS(K8-$K$3)</f>
+        <v>0.31087337089573741</v>
+      </c>
+      <c r="N8">
+        <v>5.9757199999999999</v>
+      </c>
+      <c r="O8">
+        <v>53.1509</v>
+      </c>
+      <c r="Q8">
+        <v>7.2277699999999996</v>
+      </c>
+      <c r="S8">
+        <v>3.63666</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B9" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="34" t="s">
         <v>9</v>
       </c>
       <c r="D9">
@@ -683,16 +1015,46 @@
       <c r="E9">
         <v>3.03403</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="7">
         <f t="shared" si="0"/>
         <v>5.3267940004810574</v>
       </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
+      <c r="G9">
+        <f t="shared" si="1"/>
+        <v>1.3744130481001049</v>
+      </c>
+      <c r="I9">
+        <v>1.3100499999999999</v>
+      </c>
+      <c r="J9">
+        <v>1.77512</v>
+      </c>
+      <c r="K9" s="7">
+        <f t="shared" si="2"/>
+        <v>1.3550017174916988</v>
+      </c>
+      <c r="L9">
+        <f>ABS(K9-$K$3)</f>
+        <v>0.53071256822258706</v>
+      </c>
+      <c r="N9">
+        <v>5.5556900000000002</v>
+      </c>
+      <c r="O9">
+        <v>49.4236</v>
+      </c>
+      <c r="Q9">
+        <v>6.6702199999999996</v>
+      </c>
+      <c r="S9">
+        <v>3.4113899999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B10" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="30" t="s">
         <v>5</v>
       </c>
       <c r="D10">
@@ -701,16 +1063,46 @@
       <c r="E10">
         <v>2.87385</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="7">
         <f t="shared" si="0"/>
         <v>6.8769502459942187</v>
       </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
+      <c r="G10">
+        <f t="shared" si="1"/>
+        <v>2.9245692936132661</v>
+      </c>
+      <c r="I10">
+        <v>1.0347500000000001</v>
+      </c>
+      <c r="J10">
+        <v>1.8422000000000001</v>
+      </c>
+      <c r="K10" s="7">
+        <f t="shared" si="2"/>
+        <v>1.780333413868084</v>
+      </c>
+      <c r="L10">
+        <f>ABS(K10-$K$3)</f>
+        <v>0.10538087184620193</v>
+      </c>
+      <c r="N10">
+        <v>4.9801700000000002</v>
+      </c>
+      <c r="O10">
+        <v>44.333300000000001</v>
+      </c>
+      <c r="Q10">
+        <v>6.2130999999999998</v>
+      </c>
+      <c r="S10">
+        <v>3.0224899999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B11" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="31" t="s">
         <v>6</v>
       </c>
       <c r="D11">
@@ -719,16 +1111,46 @@
       <c r="E11">
         <v>3.0214699999999999</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="7">
         <f t="shared" si="0"/>
         <v>7.1386516402641433</v>
       </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
+      <c r="G11">
+        <f t="shared" si="1"/>
+        <v>3.1862706878831908</v>
+      </c>
+      <c r="I11">
+        <v>1.06931</v>
+      </c>
+      <c r="J11">
+        <v>1.9027799999999999</v>
+      </c>
+      <c r="K11" s="7">
+        <f t="shared" si="2"/>
+        <v>1.779446558995988</v>
+      </c>
+      <c r="L11">
+        <f>ABS(K11-$K$3)</f>
+        <v>0.10626772671829787</v>
+      </c>
+      <c r="N11">
+        <v>5.1605699999999999</v>
+      </c>
+      <c r="O11">
+        <v>45.914900000000003</v>
+      </c>
+      <c r="Q11">
+        <v>6.8384499999999999</v>
+      </c>
+      <c r="S11">
+        <v>3.1656900000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B12" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D12">
@@ -737,16 +1159,46 @@
       <c r="E12">
         <v>3.28796</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="7">
         <f t="shared" si="0"/>
         <v>7.9966339792980001</v>
       </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
+      <c r="G12">
+        <f t="shared" si="1"/>
+        <v>4.0442530269170476</v>
+      </c>
+      <c r="I12">
+        <v>1.04322</v>
+      </c>
+      <c r="J12">
+        <v>2.1477499999999998</v>
+      </c>
+      <c r="K12" s="7">
+        <f t="shared" si="2"/>
+        <v>2.058769962232319</v>
+      </c>
+      <c r="L12">
+        <f>ABS(K12-$K$3)</f>
+        <v>0.17305567651803311</v>
+      </c>
+      <c r="N12">
+        <v>5.6804100000000002</v>
+      </c>
+      <c r="O12">
+        <v>50.584699999999998</v>
+      </c>
+      <c r="Q12">
+        <v>6.5793499999999998</v>
+      </c>
+      <c r="S12">
+        <v>3.37561</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="33" t="s">
         <v>8</v>
       </c>
       <c r="D13">
@@ -755,16 +1207,46 @@
       <c r="E13">
         <v>3.15388</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="7">
         <f t="shared" si="0"/>
         <v>7.2827951849517039</v>
       </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
+      <c r="G13">
+        <f t="shared" si="1"/>
+        <v>3.3304142325707513</v>
+      </c>
+      <c r="I13">
+        <v>1.0579499999999999</v>
+      </c>
+      <c r="J13">
+        <v>2.0288599999999999</v>
+      </c>
+      <c r="K13" s="7">
+        <f t="shared" si="2"/>
+        <v>1.9177276808922916</v>
+      </c>
+      <c r="L13">
+        <f>ABS(K13-$K$3)</f>
+        <v>3.2013395178005721E-2</v>
+      </c>
+      <c r="N13">
+        <v>5.4885799999999998</v>
+      </c>
+      <c r="O13">
+        <v>48.849699999999999</v>
+      </c>
+      <c r="Q13">
+        <v>6.2120899999999999</v>
+      </c>
+      <c r="S13">
+        <v>3.3210299999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B14" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="34" t="s">
         <v>9</v>
       </c>
       <c r="D14">
@@ -773,16 +1255,46 @@
       <c r="E14">
         <v>2.8599800000000002</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="7">
         <f t="shared" si="0"/>
         <v>6.0810529225404526</v>
       </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
+      <c r="G14">
+        <f t="shared" si="1"/>
+        <v>2.1286719701595</v>
+      </c>
+      <c r="I14">
+        <v>1.0791599999999999</v>
+      </c>
+      <c r="J14">
+        <v>1.8391</v>
+      </c>
+      <c r="K14" s="7">
+        <f t="shared" si="2"/>
+        <v>1.7041958560361765</v>
+      </c>
+      <c r="L14">
+        <f>ABS(K14-$K$3)</f>
+        <v>0.18151842967810938</v>
+      </c>
+      <c r="N14">
+        <v>5.0930499999999999</v>
+      </c>
+      <c r="O14">
+        <v>45.332500000000003</v>
+      </c>
+      <c r="Q14">
+        <v>5.8228099999999996</v>
+      </c>
+      <c r="S14">
+        <v>3.0944400000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B15" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="30" t="s">
         <v>5</v>
       </c>
       <c r="D15">
@@ -791,16 +1303,46 @@
       <c r="E15">
         <v>3.10778</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="7">
         <f t="shared" si="0"/>
         <v>7.3780272113688534</v>
       </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
+      <c r="G15">
+        <f t="shared" si="1"/>
+        <v>3.4256462589879009</v>
+      </c>
+      <c r="I15">
+        <v>1.04383</v>
+      </c>
+      <c r="J15">
+        <v>1.98994</v>
+      </c>
+      <c r="K15" s="7">
+        <f t="shared" si="2"/>
+        <v>1.9063832233218052</v>
+      </c>
+      <c r="L15">
+        <f>ABS(K15-$K$3)</f>
+        <v>2.0668937607519311E-2</v>
+      </c>
+      <c r="N15">
+        <v>5.4375999999999998</v>
+      </c>
+      <c r="O15">
+        <v>48.389699999999998</v>
+      </c>
+      <c r="Q15">
+        <v>5.8671300000000004</v>
+      </c>
+      <c r="S15">
+        <v>3.2338499999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B16" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="31" t="s">
         <v>6</v>
       </c>
       <c r="D16">
@@ -809,16 +1351,46 @@
       <c r="E16">
         <v>3.27474</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="7">
         <f t="shared" si="0"/>
         <v>7.5679085955157452</v>
       </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
+      <c r="G16">
+        <f t="shared" si="1"/>
+        <v>3.6155276431347927</v>
+      </c>
+      <c r="I16">
+        <v>1.09596</v>
+      </c>
+      <c r="J16">
+        <v>2.0509300000000001</v>
+      </c>
+      <c r="K16" s="7">
+        <f t="shared" si="2"/>
+        <v>1.871354793970583</v>
+      </c>
+      <c r="L16">
+        <f>ABS(K16-$K$3)</f>
+        <v>1.4359491743702879E-2</v>
+      </c>
+      <c r="N16">
+        <v>5.6488300000000002</v>
+      </c>
+      <c r="O16">
+        <v>50.260599999999997</v>
+      </c>
+      <c r="Q16">
+        <v>6.5021199999999997</v>
+      </c>
+      <c r="S16">
+        <v>3.4000300000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B17" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D17">
@@ -827,16 +1399,46 @@
       <c r="E17">
         <v>3.5846399999999998</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="7">
         <f t="shared" si="0"/>
         <v>8.6176066851456969</v>
       </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
+      <c r="G17">
+        <f t="shared" si="1"/>
+        <v>4.6652257327647444</v>
+      </c>
+      <c r="I17">
+        <v>1.05871</v>
+      </c>
+      <c r="J17">
+        <v>2.3536100000000002</v>
+      </c>
+      <c r="K17" s="7">
+        <f t="shared" si="2"/>
+        <v>2.2230922537805444</v>
+      </c>
+      <c r="L17">
+        <f>ABS(K17-$K$3)</f>
+        <v>0.33737796806625853</v>
+      </c>
+      <c r="N17">
+        <v>6.2532500000000004</v>
+      </c>
+      <c r="O17">
+        <v>55.679499999999997</v>
+      </c>
+      <c r="Q17">
+        <v>6.2925700000000004</v>
+      </c>
+      <c r="S17">
+        <v>3.6270699999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B18" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="33" t="s">
         <v>8</v>
       </c>
       <c r="D18">
@@ -845,16 +1447,46 @@
       <c r="E18">
         <v>3.4355000000000002</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="7">
         <f t="shared" si="0"/>
         <v>7.9052247426286177</v>
       </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
+      <c r="G18">
+        <f t="shared" si="1"/>
+        <v>3.9528437902476652</v>
+      </c>
+      <c r="I18">
+        <v>1.0690599999999999</v>
+      </c>
+      <c r="J18">
+        <v>2.20899</v>
+      </c>
+      <c r="K18" s="7">
+        <f t="shared" si="2"/>
+        <v>2.0662918825884424</v>
+      </c>
+      <c r="L18">
+        <f>ABS(K18-$K$3)</f>
+        <v>0.18057759687415653</v>
+      </c>
+      <c r="N18">
+        <v>6.0217299999999998</v>
+      </c>
+      <c r="O18">
+        <v>53.596299999999999</v>
+      </c>
+      <c r="Q18">
+        <v>5.9234600000000004</v>
+      </c>
+      <c r="S18">
+        <v>3.5679599999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B19" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="34" t="s">
         <v>9</v>
       </c>
       <c r="D19">
@@ -863,16 +1495,46 @@
       <c r="E19">
         <v>3.13368</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="7">
         <f t="shared" si="0"/>
         <v>6.6208190455666198</v>
       </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
+      <c r="G19">
+        <f t="shared" si="1"/>
+        <v>2.6684380931856673</v>
+      </c>
+      <c r="I19">
+        <v>1.08707</v>
+      </c>
+      <c r="J19">
+        <v>2.0002800000000001</v>
+      </c>
+      <c r="K19" s="7">
+        <f t="shared" si="2"/>
+        <v>1.8400654971620964</v>
+      </c>
+      <c r="L19">
+        <f>ABS(K19-$K$3)</f>
+        <v>4.5648788552189457E-2</v>
+      </c>
+      <c r="N19">
+        <v>5.6083999999999996</v>
+      </c>
+      <c r="O19">
+        <v>49.906300000000002</v>
+      </c>
+      <c r="Q19">
+        <v>5.5282299999999998</v>
+      </c>
+      <c r="S19">
+        <v>3.36253</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B20" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="30" t="s">
         <v>5</v>
       </c>
       <c r="D20">
@@ -881,16 +1543,46 @@
       <c r="E20">
         <v>2.9118900000000001</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="7">
         <f t="shared" si="0"/>
         <v>6.9739687740248177</v>
       </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
+      <c r="G20">
+        <f t="shared" si="1"/>
+        <v>3.0215878216438652</v>
+      </c>
+      <c r="I20">
+        <v>1.0771599999999999</v>
+      </c>
+      <c r="J20">
+        <v>1.7906899999999999</v>
+      </c>
+      <c r="K20" s="7">
+        <f t="shared" si="2"/>
+        <v>1.6624178395038807</v>
+      </c>
+      <c r="L20">
+        <f>ABS(K20-$K$3)</f>
+        <v>0.22329644621040523</v>
+      </c>
+      <c r="N20">
+        <v>5.0633999999999997</v>
+      </c>
+      <c r="O20">
+        <v>45.080599999999997</v>
+      </c>
+      <c r="Q20">
+        <v>6.5784500000000001</v>
+      </c>
+      <c r="S20">
+        <v>3.0030000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B21" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="31" t="s">
         <v>6</v>
       </c>
       <c r="D21">
@@ -899,16 +1591,46 @@
       <c r="E21">
         <v>3.06453</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="7">
         <f t="shared" si="0"/>
         <v>7.2451628461189284</v>
       </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
+      <c r="G21">
+        <f t="shared" si="1"/>
+        <v>3.2927818937379758</v>
+      </c>
+      <c r="I21">
+        <v>1.08697</v>
+      </c>
+      <c r="J21">
+        <v>1.8753</v>
+      </c>
+      <c r="K21" s="7">
+        <f t="shared" si="2"/>
+        <v>1.7252546068428751</v>
+      </c>
+      <c r="L21">
+        <f>ABS(K21-$K$3)</f>
+        <v>0.16045967887141077</v>
+      </c>
+      <c r="N21">
+        <v>5.2403000000000004</v>
+      </c>
+      <c r="O21">
+        <v>46.636099999999999</v>
+      </c>
+      <c r="Q21">
+        <v>7.1804199999999998</v>
+      </c>
+      <c r="S21">
+        <v>3.1513800000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B22" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D22">
@@ -917,16 +1639,46 @@
       <c r="E22">
         <v>3.3502000000000001</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="7">
         <f t="shared" si="0"/>
         <v>7.9937962300167031</v>
       </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
+      <c r="G22">
+        <f t="shared" si="1"/>
+        <v>4.0414152776357506</v>
+      </c>
+      <c r="I22">
+        <v>1.08958</v>
+      </c>
+      <c r="J22">
+        <v>2.1211799999999998</v>
+      </c>
+      <c r="K22" s="7">
+        <f t="shared" si="2"/>
+        <v>1.9467868352943334</v>
+      </c>
+      <c r="L22">
+        <f>ABS(K22-$K$3)</f>
+        <v>6.1072549580047486E-2</v>
+      </c>
+      <c r="N22">
+        <v>5.8003</v>
+      </c>
+      <c r="O22">
+        <v>51.6477</v>
+      </c>
+      <c r="Q22">
+        <v>7.11965</v>
+      </c>
+      <c r="S22">
+        <v>3.3783300000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B23" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="33" t="s">
         <v>8</v>
       </c>
       <c r="D23">
@@ -935,40 +1687,85 @@
       <c r="E23">
         <v>3.2103999999999999</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="7">
         <f t="shared" si="0"/>
         <v>7.4654909402090999</v>
       </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B24" t="s">
+      <c r="G23">
+        <f t="shared" si="1"/>
+        <v>3.5131099878281473</v>
+      </c>
+      <c r="I23">
+        <v>1.10812</v>
+      </c>
+      <c r="J23">
+        <v>1.9831399999999999</v>
+      </c>
+      <c r="K23" s="7">
+        <f t="shared" si="2"/>
+        <v>1.7896437208966538</v>
+      </c>
+      <c r="L23">
+        <f>ABS(K23-$K$3)</f>
+        <v>9.6070564817632098E-2</v>
+      </c>
+      <c r="N23">
+        <v>5.5898399999999997</v>
+      </c>
+      <c r="O23">
+        <v>49.747799999999998</v>
+      </c>
+      <c r="Q23">
+        <v>6.6969900000000004</v>
+      </c>
+      <c r="S23">
+        <v>3.2955700000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B24" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="34" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
+      <c r="F24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="S24">
+        <v>3.1013899999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B25" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="30" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
+      <c r="F25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="S25">
+        <v>5.37791</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B26" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="31" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
+      <c r="F26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="S26">
+        <v>5.5034900000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B27" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D27">
@@ -977,32 +1774,72 @@
       <c r="E27">
         <v>4.9477700000000002</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="7">
         <f t="shared" si="0"/>
         <v>6.2307578001430572</v>
       </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
+      <c r="G27">
+        <f t="shared" si="1"/>
+        <v>2.2783768477621047</v>
+      </c>
+      <c r="I27">
+        <v>1.1999899999999999</v>
+      </c>
+      <c r="J27">
+        <v>3.2099799999999998</v>
+      </c>
+      <c r="K27" s="7">
+        <f>J27/I27</f>
+        <v>2.6750056250468757</v>
+      </c>
+      <c r="L27">
+        <f>ABS(K27-$K$3)</f>
+        <v>0.78929133933258977</v>
+      </c>
+      <c r="N27">
+        <v>8.0787600000000008</v>
+      </c>
+      <c r="O27">
+        <v>71.751199999999997</v>
+      </c>
+      <c r="Q27">
+        <v>9.5980699999999999</v>
+      </c>
+      <c r="S27">
+        <v>5.9730800000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B28" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="33" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
+      <c r="F28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="S28">
+        <v>5.8974399999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B29" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="34" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
+      <c r="F29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="S29">
+        <v>5.5428899999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B30" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="30" t="s">
         <v>5</v>
       </c>
       <c r="D30">
@@ -1011,16 +1848,46 @@
       <c r="E30">
         <v>3.65578</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="7">
         <f t="shared" si="0"/>
         <v>6.07450018610092</v>
       </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B31" t="s">
+      <c r="G30">
+        <f t="shared" si="1"/>
+        <v>2.1221192337199675</v>
+      </c>
+      <c r="I30">
+        <v>1.3165899999999999</v>
+      </c>
+      <c r="J30">
+        <v>2.1745299999999999</v>
+      </c>
+      <c r="K30" s="7">
+        <f>J30/I30</f>
+        <v>1.6516379434751898</v>
+      </c>
+      <c r="L30">
+        <f>ABS(K30-$K$3)</f>
+        <v>0.23407634223909612</v>
+      </c>
+      <c r="N30">
+        <v>6.2786799999999996</v>
+      </c>
+      <c r="O30">
+        <v>55.801600000000001</v>
+      </c>
+      <c r="Q30">
+        <v>7.3128000000000002</v>
+      </c>
+      <c r="S30">
+        <v>4.1921200000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B31" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="31" t="s">
         <v>6</v>
       </c>
       <c r="D31">
@@ -1029,16 +1896,46 @@
       <c r="E31">
         <v>3.8193000000000001</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="7">
         <f t="shared" si="0"/>
         <v>6.2310851090558179</v>
       </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
+      <c r="G31">
+        <f t="shared" si="1"/>
+        <v>2.2787041566748654</v>
+      </c>
+      <c r="I31">
+        <v>1.3347599999999999</v>
+      </c>
+      <c r="J31">
+        <v>2.2566999999999999</v>
+      </c>
+      <c r="K31" s="7">
+        <f t="shared" ref="K31:K39" si="3">J31/I31</f>
+        <v>1.6907159339506728</v>
+      </c>
+      <c r="L31">
+        <f>ABS(K31-$K$3)</f>
+        <v>0.19499835176361313</v>
+      </c>
+      <c r="N31">
+        <v>6.47417</v>
+      </c>
+      <c r="O31">
+        <v>57.527500000000003</v>
+      </c>
+      <c r="Q31">
+        <v>7.96922</v>
+      </c>
+      <c r="S31">
+        <v>4.3635700000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B32" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D32">
@@ -1047,16 +1944,46 @@
       <c r="E32">
         <v>4.1832799999999999</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="7">
         <f t="shared" si="0"/>
         <v>7.0630942149988254</v>
       </c>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
+      <c r="G32">
+        <f t="shared" si="1"/>
+        <v>3.1107132626178728</v>
+      </c>
+      <c r="I32">
+        <v>1.3169500000000001</v>
+      </c>
+      <c r="J32">
+        <v>2.5416500000000002</v>
+      </c>
+      <c r="K32" s="7">
+        <f t="shared" si="3"/>
+        <v>1.9299517825278105</v>
+      </c>
+      <c r="L32">
+        <f>ABS(K32-$K$3)</f>
+        <v>4.4237496813524624E-2</v>
+      </c>
+      <c r="N32">
+        <v>7.09924</v>
+      </c>
+      <c r="O32">
+        <v>63.089700000000001</v>
+      </c>
+      <c r="Q32">
+        <v>7.7538099999999996</v>
+      </c>
+      <c r="S32">
+        <v>4.6770899999999997</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B33" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="33" t="s">
         <v>8</v>
       </c>
       <c r="D33">
@@ -1065,16 +1992,46 @@
       <c r="E33">
         <v>3.9975299999999998</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="7">
         <f t="shared" si="0"/>
         <v>6.3167999544909383</v>
       </c>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B34" t="s">
+      <c r="G33">
+        <f t="shared" si="1"/>
+        <v>2.3644190021099858</v>
+      </c>
+      <c r="I33">
+        <v>1.35507</v>
+      </c>
+      <c r="J33">
+        <v>2.3805399999999999</v>
+      </c>
+      <c r="K33" s="7">
+        <f t="shared" si="3"/>
+        <v>1.7567653331562205</v>
+      </c>
+      <c r="L33">
+        <f>ABS(K33-$K$3)</f>
+        <v>0.12894895255806538</v>
+      </c>
+      <c r="N33">
+        <v>6.89642</v>
+      </c>
+      <c r="O33">
+        <v>61.3001</v>
+      </c>
+      <c r="Q33">
+        <v>7.3190099999999996</v>
+      </c>
+      <c r="S33">
+        <v>4.6220999999999997</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B34" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="34" t="s">
         <v>9</v>
       </c>
       <c r="D34">
@@ -1083,16 +2040,46 @@
       <c r="E34">
         <v>3.6390099999999999</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="7">
         <f t="shared" si="0"/>
         <v>5.4683717400614604</v>
       </c>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
+      <c r="G34">
+        <f t="shared" si="1"/>
+        <v>1.5159907876805079</v>
+      </c>
+      <c r="I34">
+        <v>1.3777699999999999</v>
+      </c>
+      <c r="J34">
+        <v>2.1577799999999998</v>
+      </c>
+      <c r="K34" s="7">
+        <f t="shared" si="3"/>
+        <v>1.5661394862712934</v>
+      </c>
+      <c r="L34">
+        <f>ABS(K34-$K$3)</f>
+        <v>0.3195747994429925</v>
+      </c>
+      <c r="N34">
+        <v>6.4173200000000001</v>
+      </c>
+      <c r="O34">
+        <v>57.0227</v>
+      </c>
+      <c r="Q34">
+        <v>6.8226199999999997</v>
+      </c>
+      <c r="S34">
+        <v>4.3030999999999997</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B35" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="30" t="s">
         <v>5</v>
       </c>
       <c r="D35">
@@ -1101,16 +2088,46 @@
       <c r="E35">
         <v>3.1156899999999998</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="7">
         <f t="shared" si="0"/>
         <v>6.8001885734115852</v>
       </c>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
+      <c r="G35">
+        <f t="shared" si="1"/>
+        <v>2.8478076210306327</v>
+      </c>
+      <c r="I35">
+        <v>1.12341</v>
+      </c>
+      <c r="J35">
+        <v>2.0160399999999998</v>
+      </c>
+      <c r="K35" s="7">
+        <f t="shared" si="3"/>
+        <v>1.7945718838180182</v>
+      </c>
+      <c r="L35">
+        <f>ABS(K35-$K$3)</f>
+        <v>9.1142401896267655E-2</v>
+      </c>
+      <c r="N35">
+        <v>5.6448900000000002</v>
+      </c>
+      <c r="O35">
+        <v>50.250799999999998</v>
+      </c>
+      <c r="Q35">
+        <v>5.8958000000000004</v>
+      </c>
+      <c r="S35">
+        <v>3.2874099999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B36" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="31" t="s">
         <v>6</v>
       </c>
       <c r="D36">
@@ -1119,16 +2136,46 @@
       <c r="E36">
         <v>3.28783</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="7">
         <f t="shared" si="0"/>
         <v>6.8423188502312104</v>
       </c>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
+      <c r="G36">
+        <f t="shared" si="1"/>
+        <v>2.8899378978502579</v>
+      </c>
+      <c r="I36">
+        <v>1.20478</v>
+      </c>
+      <c r="J36">
+        <v>2.0672299999999999</v>
+      </c>
+      <c r="K36" s="7">
+        <f t="shared" si="3"/>
+        <v>1.7158568369328839</v>
+      </c>
+      <c r="L36">
+        <f>ABS(K36-$K$3)</f>
+        <v>0.16985744878140197</v>
+      </c>
+      <c r="N36">
+        <v>5.9012500000000001</v>
+      </c>
+      <c r="O36">
+        <v>52.503700000000002</v>
+      </c>
+      <c r="Q36">
+        <v>6.6056400000000002</v>
+      </c>
+      <c r="S36">
+        <v>3.4754</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B37" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D37">
@@ -1137,16 +2184,46 @@
       <c r="E37">
         <v>3.6107</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="7">
         <f t="shared" si="0"/>
         <v>8.2110256561861839</v>
       </c>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
+      <c r="G37">
+        <f t="shared" si="1"/>
+        <v>4.2586447038052313</v>
+      </c>
+      <c r="I37">
+        <v>1.14232</v>
+      </c>
+      <c r="J37">
+        <v>2.40422</v>
+      </c>
+      <c r="K37" s="7">
+        <f t="shared" si="3"/>
+        <v>2.1046817003991878</v>
+      </c>
+      <c r="L37">
+        <f>ABS(K37-$K$3)</f>
+        <v>0.21896741468490188</v>
+      </c>
+      <c r="N37">
+        <v>6.53972</v>
+      </c>
+      <c r="O37">
+        <v>58.223300000000002</v>
+      </c>
+      <c r="Q37">
+        <v>6.3208900000000003</v>
+      </c>
+      <c r="S37">
+        <v>3.6525599999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B38" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="33" t="s">
         <v>8</v>
       </c>
       <c r="D38">
@@ -1155,16 +2232,46 @@
       <c r="E38">
         <v>3.4268700000000001</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="7">
         <f t="shared" si="0"/>
         <v>7.3602424440282483</v>
       </c>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
+      <c r="G38">
+        <f t="shared" si="1"/>
+        <v>3.4078614916472958</v>
+      </c>
+      <c r="I38">
+        <v>1.1450499999999999</v>
+      </c>
+      <c r="J38">
+        <v>2.23062</v>
+      </c>
+      <c r="K38" s="7">
+        <f t="shared" si="3"/>
+        <v>1.9480546701017425</v>
+      </c>
+      <c r="L38">
+        <f>ABS(K38-$K$3)</f>
+        <v>6.2340384387456593E-2</v>
+      </c>
+      <c r="N38">
+        <v>6.2171799999999999</v>
+      </c>
+      <c r="O38">
+        <v>55.320500000000003</v>
+      </c>
+      <c r="Q38">
+        <v>5.9209100000000001</v>
+      </c>
+      <c r="S38">
+        <v>3.5979000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B39" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="34" t="s">
         <v>9</v>
       </c>
       <c r="D39">
@@ -1173,12 +2280,62 @@
       <c r="E39">
         <v>3.1228099999999999</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="8">
         <f t="shared" si="0"/>
         <v>6.1639233597893508</v>
       </c>
+      <c r="G39">
+        <f t="shared" si="1"/>
+        <v>2.2115424074083982</v>
+      </c>
+      <c r="I39">
+        <v>1.14564</v>
+      </c>
+      <c r="J39">
+        <v>2.0194000000000001</v>
+      </c>
+      <c r="K39" s="8">
+        <f t="shared" si="3"/>
+        <v>1.7626828672183235</v>
+      </c>
+      <c r="L39">
+        <f>ABS(K39-$K$3)</f>
+        <v>0.12303141849596244</v>
+      </c>
+      <c r="N39">
+        <v>5.7396599999999998</v>
+      </c>
+      <c r="O39">
+        <v>51.0578</v>
+      </c>
+      <c r="Q39">
+        <v>5.5046499999999998</v>
+      </c>
+      <c r="S39">
+        <v>3.3994900000000001</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="G5:G39">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L5:L39">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/analysis/corrected_working/SF_18O_18F.xlsx
+++ b/analysis/corrected_working/SF_18O_18F.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kawecka/digios/analysis/corrected_working/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888F6C3F-4D93-9F45-B70E-1A7FEB94C52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{060E8E9A-18E0-C64F-BAFC-F3D1121B1056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17220" xr2:uid="{3ABE6ABB-8332-1E45-BF21-9E3D8711C9F0}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17220" activeTab="1" xr2:uid="{3ABE6ABB-8332-1E45-BF21-9E3D8711C9F0}"/>
   </bookViews>
   <sheets>
     <sheet name="18O" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="32">
   <si>
     <t>1,982 MeV</t>
   </si>
@@ -125,22 +125,24 @@
   <si>
     <t>0 MeV (gs)</t>
   </si>
+  <si>
+    <t>literature (O)</t>
+  </si>
+  <si>
+    <t>4652 keV</t>
+  </si>
+  <si>
+    <t>4753 keV</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -344,7 +346,6 @@
   </cellStyleXfs>
   <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -379,6 +380,7 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -713,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC19792A-629E-104B-BC7C-CEC29C61C0D2}">
-  <dimension ref="B1:S39"/>
+  <dimension ref="B1:S40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="4.1640625" customWidth="1"/>
@@ -724,31 +726,31 @@
   <sheetData>
     <row r="1" spans="2:19" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J2" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="S2" s="4" t="s">
         <v>28</v>
       </c>
     </row>
@@ -756,11 +758,11 @@
       <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <f>0.83/0.21</f>
         <v>3.9523809523809526</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="2">
         <f>0.66/0.35</f>
         <v>1.8857142857142859</v>
       </c>
@@ -772,49 +774,49 @@
       </c>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="35"/>
-      <c r="I4" s="4" t="s">
+      <c r="H4" s="34"/>
+      <c r="I4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="35" t="s">
+      <c r="L4" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="Q4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="S4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="29" t="s">
         <v>5</v>
       </c>
       <c r="D5">
@@ -823,7 +825,7 @@
       <c r="E5">
         <v>3.0304000000000002</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <f>E5/D5</f>
         <v>5.9448282897240627</v>
       </c>
@@ -837,7 +839,7 @@
       <c r="J5">
         <v>1.80183</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <f>J5/I5</f>
         <v>1.4641882008776208</v>
       </c>
@@ -859,10 +861,10 @@
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="30" t="s">
         <v>6</v>
       </c>
       <c r="D6">
@@ -871,12 +873,12 @@
       <c r="E6">
         <v>3.1882600000000001</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <f t="shared" ref="F6:F39" si="0">E6/D6</f>
         <v>6.1273689247805727</v>
       </c>
       <c r="G6">
-        <f t="shared" ref="G6:G39" si="1">ABS(F6-$F$3)</f>
+        <f t="shared" ref="G6:G40" si="1">ABS(F6-$F$3)</f>
         <v>2.1749879723996202</v>
       </c>
       <c r="I6">
@@ -885,7 +887,7 @@
       <c r="J6">
         <v>1.8972</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="6">
         <f>J6/I6</f>
         <v>1.5383367929423977</v>
       </c>
@@ -907,10 +909,10 @@
       </c>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="31" t="s">
         <v>7</v>
       </c>
       <c r="D7">
@@ -919,7 +921,7 @@
       <c r="E7">
         <v>3.51823</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <f t="shared" si="0"/>
         <v>6.9105362091960298</v>
       </c>
@@ -933,7 +935,7 @@
       <c r="J7">
         <v>2.1539899999999998</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="6">
         <f t="shared" ref="K7:K23" si="2">J7/I7</f>
         <v>1.7306406774758558</v>
       </c>
@@ -955,10 +957,10 @@
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="32" t="s">
         <v>8</v>
       </c>
       <c r="D8">
@@ -967,7 +969,7 @@
       <c r="E8">
         <v>3.3570099999999998</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <f t="shared" si="0"/>
         <v>6.4035869136023829</v>
       </c>
@@ -981,7 +983,7 @@
       <c r="J8">
         <v>1.9996700000000001</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="6">
         <f t="shared" si="2"/>
         <v>1.5748409148185485</v>
       </c>
@@ -1003,10 +1005,10 @@
       </c>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="33" t="s">
         <v>9</v>
       </c>
       <c r="D9">
@@ -1015,7 +1017,7 @@
       <c r="E9">
         <v>3.03403</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <f t="shared" si="0"/>
         <v>5.3267940004810574</v>
       </c>
@@ -1029,7 +1031,7 @@
       <c r="J9">
         <v>1.77512</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="6">
         <f t="shared" si="2"/>
         <v>1.3550017174916988</v>
       </c>
@@ -1051,10 +1053,10 @@
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="29" t="s">
         <v>5</v>
       </c>
       <c r="D10">
@@ -1063,7 +1065,7 @@
       <c r="E10">
         <v>2.87385</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="6">
         <f t="shared" si="0"/>
         <v>6.8769502459942187</v>
       </c>
@@ -1077,7 +1079,7 @@
       <c r="J10">
         <v>1.8422000000000001</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="6">
         <f t="shared" si="2"/>
         <v>1.780333413868084</v>
       </c>
@@ -1099,10 +1101,10 @@
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="30" t="s">
         <v>6</v>
       </c>
       <c r="D11">
@@ -1111,7 +1113,7 @@
       <c r="E11">
         <v>3.0214699999999999</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <f t="shared" si="0"/>
         <v>7.1386516402641433</v>
       </c>
@@ -1125,7 +1127,7 @@
       <c r="J11">
         <v>1.9027799999999999</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="6">
         <f t="shared" si="2"/>
         <v>1.779446558995988</v>
       </c>
@@ -1147,10 +1149,10 @@
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="31" t="s">
         <v>7</v>
       </c>
       <c r="D12">
@@ -1159,7 +1161,7 @@
       <c r="E12">
         <v>3.28796</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <f t="shared" si="0"/>
         <v>7.9966339792980001</v>
       </c>
@@ -1173,7 +1175,7 @@
       <c r="J12">
         <v>2.1477499999999998</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="6">
         <f t="shared" si="2"/>
         <v>2.058769962232319</v>
       </c>
@@ -1195,10 +1197,10 @@
       </c>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="32" t="s">
         <v>8</v>
       </c>
       <c r="D13">
@@ -1207,7 +1209,7 @@
       <c r="E13">
         <v>3.15388</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <f t="shared" si="0"/>
         <v>7.2827951849517039</v>
       </c>
@@ -1221,7 +1223,7 @@
       <c r="J13">
         <v>2.0288599999999999</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K13" s="6">
         <f t="shared" si="2"/>
         <v>1.9177276808922916</v>
       </c>
@@ -1243,10 +1245,10 @@
       </c>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="33" t="s">
         <v>9</v>
       </c>
       <c r="D14">
@@ -1255,7 +1257,7 @@
       <c r="E14">
         <v>2.8599800000000002</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="6">
         <f t="shared" si="0"/>
         <v>6.0810529225404526</v>
       </c>
@@ -1269,7 +1271,7 @@
       <c r="J14">
         <v>1.8391</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K14" s="6">
         <f t="shared" si="2"/>
         <v>1.7041958560361765</v>
       </c>
@@ -1291,10 +1293,10 @@
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="29" t="s">
         <v>5</v>
       </c>
       <c r="D15">
@@ -1303,7 +1305,7 @@
       <c r="E15">
         <v>3.10778</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="6">
         <f t="shared" si="0"/>
         <v>7.3780272113688534</v>
       </c>
@@ -1317,7 +1319,7 @@
       <c r="J15">
         <v>1.98994</v>
       </c>
-      <c r="K15" s="7">
+      <c r="K15" s="6">
         <f t="shared" si="2"/>
         <v>1.9063832233218052</v>
       </c>
@@ -1339,10 +1341,10 @@
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="30" t="s">
         <v>6</v>
       </c>
       <c r="D16">
@@ -1351,7 +1353,7 @@
       <c r="E16">
         <v>3.27474</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="6">
         <f t="shared" si="0"/>
         <v>7.5679085955157452</v>
       </c>
@@ -1365,7 +1367,7 @@
       <c r="J16">
         <v>2.0509300000000001</v>
       </c>
-      <c r="K16" s="7">
+      <c r="K16" s="6">
         <f t="shared" si="2"/>
         <v>1.871354793970583</v>
       </c>
@@ -1387,10 +1389,10 @@
       </c>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="31" t="s">
         <v>7</v>
       </c>
       <c r="D17">
@@ -1399,7 +1401,7 @@
       <c r="E17">
         <v>3.5846399999999998</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="6">
         <f t="shared" si="0"/>
         <v>8.6176066851456969</v>
       </c>
@@ -1413,7 +1415,7 @@
       <c r="J17">
         <v>2.3536100000000002</v>
       </c>
-      <c r="K17" s="7">
+      <c r="K17" s="6">
         <f t="shared" si="2"/>
         <v>2.2230922537805444</v>
       </c>
@@ -1435,10 +1437,10 @@
       </c>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="32" t="s">
         <v>8</v>
       </c>
       <c r="D18">
@@ -1447,7 +1449,7 @@
       <c r="E18">
         <v>3.4355000000000002</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="6">
         <f t="shared" si="0"/>
         <v>7.9052247426286177</v>
       </c>
@@ -1461,7 +1463,7 @@
       <c r="J18">
         <v>2.20899</v>
       </c>
-      <c r="K18" s="7">
+      <c r="K18" s="6">
         <f t="shared" si="2"/>
         <v>2.0662918825884424</v>
       </c>
@@ -1483,10 +1485,10 @@
       </c>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="33" t="s">
         <v>9</v>
       </c>
       <c r="D19">
@@ -1495,7 +1497,7 @@
       <c r="E19">
         <v>3.13368</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="6">
         <f t="shared" si="0"/>
         <v>6.6208190455666198</v>
       </c>
@@ -1509,7 +1511,7 @@
       <c r="J19">
         <v>2.0002800000000001</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K19" s="6">
         <f t="shared" si="2"/>
         <v>1.8400654971620964</v>
       </c>
@@ -1531,10 +1533,10 @@
       </c>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="29" t="s">
         <v>5</v>
       </c>
       <c r="D20">
@@ -1543,7 +1545,7 @@
       <c r="E20">
         <v>2.9118900000000001</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="6">
         <f t="shared" si="0"/>
         <v>6.9739687740248177</v>
       </c>
@@ -1557,7 +1559,7 @@
       <c r="J20">
         <v>1.7906899999999999</v>
       </c>
-      <c r="K20" s="7">
+      <c r="K20" s="6">
         <f t="shared" si="2"/>
         <v>1.6624178395038807</v>
       </c>
@@ -1579,10 +1581,10 @@
       </c>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="30" t="s">
         <v>6</v>
       </c>
       <c r="D21">
@@ -1591,7 +1593,7 @@
       <c r="E21">
         <v>3.06453</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="6">
         <f t="shared" si="0"/>
         <v>7.2451628461189284</v>
       </c>
@@ -1605,7 +1607,7 @@
       <c r="J21">
         <v>1.8753</v>
       </c>
-      <c r="K21" s="7">
+      <c r="K21" s="6">
         <f t="shared" si="2"/>
         <v>1.7252546068428751</v>
       </c>
@@ -1627,10 +1629,10 @@
       </c>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C22" s="31" t="s">
         <v>7</v>
       </c>
       <c r="D22">
@@ -1639,7 +1641,7 @@
       <c r="E22">
         <v>3.3502000000000001</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="6">
         <f t="shared" si="0"/>
         <v>7.9937962300167031</v>
       </c>
@@ -1653,7 +1655,7 @@
       <c r="J22">
         <v>2.1211799999999998</v>
       </c>
-      <c r="K22" s="7">
+      <c r="K22" s="6">
         <f t="shared" si="2"/>
         <v>1.9467868352943334</v>
       </c>
@@ -1675,10 +1677,10 @@
       </c>
     </row>
     <row r="23" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="32" t="s">
         <v>8</v>
       </c>
       <c r="D23">
@@ -1687,7 +1689,7 @@
       <c r="E23">
         <v>3.2103999999999999</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="6">
         <f t="shared" si="0"/>
         <v>7.4654909402090999</v>
       </c>
@@ -1701,7 +1703,7 @@
       <c r="J23">
         <v>1.9831399999999999</v>
       </c>
-      <c r="K23" s="7">
+      <c r="K23" s="6">
         <f t="shared" si="2"/>
         <v>1.7896437208966538</v>
       </c>
@@ -1723,49 +1725,49 @@
       </c>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="F24" s="7"/>
-      <c r="K24" s="7"/>
+      <c r="F24" s="6"/>
+      <c r="K24" s="6"/>
       <c r="S24">
         <v>3.1013899999999999</v>
       </c>
     </row>
     <row r="25" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="30" t="s">
+      <c r="C25" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="F25" s="7"/>
-      <c r="K25" s="7"/>
+      <c r="F25" s="6"/>
+      <c r="K25" s="6"/>
       <c r="S25">
         <v>5.37791</v>
       </c>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="31" t="s">
+      <c r="C26" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F26" s="7"/>
-      <c r="K26" s="7"/>
+      <c r="F26" s="6"/>
+      <c r="K26" s="6"/>
       <c r="S26">
         <v>5.5034900000000002</v>
       </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="32" t="s">
+      <c r="C27" s="31" t="s">
         <v>7</v>
       </c>
       <c r="D27">
@@ -1774,7 +1776,7 @@
       <c r="E27">
         <v>4.9477700000000002</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="6">
         <f t="shared" si="0"/>
         <v>6.2307578001430572</v>
       </c>
@@ -1788,7 +1790,7 @@
       <c r="J27">
         <v>3.2099799999999998</v>
       </c>
-      <c r="K27" s="7">
+      <c r="K27" s="6">
         <f>J27/I27</f>
         <v>2.6750056250468757</v>
       </c>
@@ -1810,36 +1812,36 @@
       </c>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="7"/>
-      <c r="K28" s="7"/>
+      <c r="F28" s="6"/>
+      <c r="K28" s="6"/>
       <c r="S28">
         <v>5.8974399999999996</v>
       </c>
     </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="F29" s="7"/>
-      <c r="K29" s="7"/>
+      <c r="F29" s="6"/>
+      <c r="K29" s="6"/>
       <c r="S29">
         <v>5.5428899999999999</v>
       </c>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="30" t="s">
+      <c r="C30" s="29" t="s">
         <v>5</v>
       </c>
       <c r="D30">
@@ -1848,7 +1850,7 @@
       <c r="E30">
         <v>3.65578</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="6">
         <f t="shared" si="0"/>
         <v>6.07450018610092</v>
       </c>
@@ -1862,7 +1864,7 @@
       <c r="J30">
         <v>2.1745299999999999</v>
       </c>
-      <c r="K30" s="7">
+      <c r="K30" s="6">
         <f>J30/I30</f>
         <v>1.6516379434751898</v>
       </c>
@@ -1884,10 +1886,10 @@
       </c>
     </row>
     <row r="31" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="31" t="s">
+      <c r="C31" s="30" t="s">
         <v>6</v>
       </c>
       <c r="D31">
@@ -1896,7 +1898,7 @@
       <c r="E31">
         <v>3.8193000000000001</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="6">
         <f t="shared" si="0"/>
         <v>6.2310851090558179</v>
       </c>
@@ -1910,7 +1912,7 @@
       <c r="J31">
         <v>2.2566999999999999</v>
       </c>
-      <c r="K31" s="7">
+      <c r="K31" s="6">
         <f t="shared" ref="K31:K39" si="3">J31/I31</f>
         <v>1.6907159339506728</v>
       </c>
@@ -1932,10 +1934,10 @@
       </c>
     </row>
     <row r="32" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B32" s="25" t="s">
+      <c r="B32" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="31" t="s">
         <v>7</v>
       </c>
       <c r="D32">
@@ -1944,7 +1946,7 @@
       <c r="E32">
         <v>4.1832799999999999</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="6">
         <f t="shared" si="0"/>
         <v>7.0630942149988254</v>
       </c>
@@ -1958,7 +1960,7 @@
       <c r="J32">
         <v>2.5416500000000002</v>
       </c>
-      <c r="K32" s="7">
+      <c r="K32" s="6">
         <f t="shared" si="3"/>
         <v>1.9299517825278105</v>
       </c>
@@ -1980,10 +1982,10 @@
       </c>
     </row>
     <row r="33" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="C33" s="32" t="s">
         <v>8</v>
       </c>
       <c r="D33">
@@ -1992,7 +1994,7 @@
       <c r="E33">
         <v>3.9975299999999998</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="6">
         <f t="shared" si="0"/>
         <v>6.3167999544909383</v>
       </c>
@@ -2006,7 +2008,7 @@
       <c r="J33">
         <v>2.3805399999999999</v>
       </c>
-      <c r="K33" s="7">
+      <c r="K33" s="6">
         <f t="shared" si="3"/>
         <v>1.7567653331562205</v>
       </c>
@@ -2028,10 +2030,10 @@
       </c>
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="34" t="s">
+      <c r="C34" s="33" t="s">
         <v>9</v>
       </c>
       <c r="D34">
@@ -2040,7 +2042,7 @@
       <c r="E34">
         <v>3.6390099999999999</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="6">
         <f t="shared" si="0"/>
         <v>5.4683717400614604</v>
       </c>
@@ -2054,7 +2056,7 @@
       <c r="J34">
         <v>2.1577799999999998</v>
       </c>
-      <c r="K34" s="7">
+      <c r="K34" s="6">
         <f t="shared" si="3"/>
         <v>1.5661394862712934</v>
       </c>
@@ -2076,10 +2078,10 @@
       </c>
     </row>
     <row r="35" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B35" s="27" t="s">
+      <c r="B35" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="30" t="s">
+      <c r="C35" s="29" t="s">
         <v>5</v>
       </c>
       <c r="D35">
@@ -2088,7 +2090,7 @@
       <c r="E35">
         <v>3.1156899999999998</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="6">
         <f t="shared" si="0"/>
         <v>6.8001885734115852</v>
       </c>
@@ -2102,7 +2104,7 @@
       <c r="J35">
         <v>2.0160399999999998</v>
       </c>
-      <c r="K35" s="7">
+      <c r="K35" s="6">
         <f t="shared" si="3"/>
         <v>1.7945718838180182</v>
       </c>
@@ -2124,10 +2126,10 @@
       </c>
     </row>
     <row r="36" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B36" s="28" t="s">
+      <c r="B36" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="31" t="s">
+      <c r="C36" s="30" t="s">
         <v>6</v>
       </c>
       <c r="D36">
@@ -2136,7 +2138,7 @@
       <c r="E36">
         <v>3.28783</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F36" s="6">
         <f t="shared" si="0"/>
         <v>6.8423188502312104</v>
       </c>
@@ -2150,7 +2152,7 @@
       <c r="J36">
         <v>2.0672299999999999</v>
       </c>
-      <c r="K36" s="7">
+      <c r="K36" s="6">
         <f t="shared" si="3"/>
         <v>1.7158568369328839</v>
       </c>
@@ -2172,10 +2174,10 @@
       </c>
     </row>
     <row r="37" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="32" t="s">
+      <c r="C37" s="31" t="s">
         <v>7</v>
       </c>
       <c r="D37">
@@ -2184,7 +2186,7 @@
       <c r="E37">
         <v>3.6107</v>
       </c>
-      <c r="F37" s="7">
+      <c r="F37" s="6">
         <f t="shared" si="0"/>
         <v>8.2110256561861839</v>
       </c>
@@ -2198,7 +2200,7 @@
       <c r="J37">
         <v>2.40422</v>
       </c>
-      <c r="K37" s="7">
+      <c r="K37" s="6">
         <f t="shared" si="3"/>
         <v>2.1046817003991878</v>
       </c>
@@ -2220,10 +2222,10 @@
       </c>
     </row>
     <row r="38" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B38" s="28" t="s">
+      <c r="B38" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C38" s="33" t="s">
+      <c r="C38" s="32" t="s">
         <v>8</v>
       </c>
       <c r="D38">
@@ -2232,7 +2234,7 @@
       <c r="E38">
         <v>3.4268700000000001</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38" s="6">
         <f t="shared" si="0"/>
         <v>7.3602424440282483</v>
       </c>
@@ -2246,7 +2248,7 @@
       <c r="J38">
         <v>2.23062</v>
       </c>
-      <c r="K38" s="7">
+      <c r="K38" s="6">
         <f t="shared" si="3"/>
         <v>1.9480546701017425</v>
       </c>
@@ -2268,10 +2270,10 @@
       </c>
     </row>
     <row r="39" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B39" s="29" t="s">
+      <c r="B39" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="34" t="s">
+      <c r="C39" s="33" t="s">
         <v>9</v>
       </c>
       <c r="D39">
@@ -2280,7 +2282,7 @@
       <c r="E39">
         <v>3.1228099999999999</v>
       </c>
-      <c r="F39" s="8">
+      <c r="F39" s="7">
         <f t="shared" si="0"/>
         <v>6.1639233597893508</v>
       </c>
@@ -2294,7 +2296,7 @@
       <c r="J39">
         <v>2.0194000000000001</v>
       </c>
-      <c r="K39" s="8">
+      <c r="K39" s="7">
         <f t="shared" si="3"/>
         <v>1.7626828672183235</v>
       </c>
@@ -2315,8 +2317,18 @@
         <v>3.3994900000000001</v>
       </c>
     </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="F40" s="35">
+        <f>AVERAGE(F5:F23,F27,F30:F39)</f>
+        <v>6.8873170423308441</v>
+      </c>
+      <c r="K40" s="35">
+        <f>AVERAGE(K5:K23,K27,K30:K39)</f>
+        <v>1.8176945497296801</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="G5:G39">
+  <conditionalFormatting sqref="G5:G40">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -2326,7 +2338,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L5:L39">
+  <conditionalFormatting sqref="L5:L40">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -2342,7 +2354,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37E2BDE-B4E4-A647-A4B3-5C71D5BC4EFD}">
-  <dimension ref="B2:G40"/>
+  <dimension ref="B2:Q41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="4.1640625" customWidth="1"/>
@@ -2350,36 +2362,77 @@
     <col min="6" max="6" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="2:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="5" t="s">
+    <row r="2" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="J3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.2">
       <c r="D4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D5" s="4" t="s">
+      <c r="F4" s="2">
+        <f>0.83/0.21</f>
+        <v>3.9523809523809526</v>
+      </c>
+      <c r="K4" s="2">
+        <f>0.66/0.35</f>
+        <v>1.8857142857142859</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="D5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
+      <c r="I5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="29" t="s">
         <v>5</v>
       </c>
       <c r="D6">
@@ -2392,12 +2445,28 @@
         <f>E6/D6</f>
         <v>8.6989399416705968</v>
       </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
+      <c r="I6">
+        <v>0.60964700000000005</v>
+      </c>
+      <c r="J6">
+        <v>0.70172100000000004</v>
+      </c>
+      <c r="K6">
+        <f>J6/I6</f>
+        <v>1.1510283819981071</v>
+      </c>
+      <c r="N6">
+        <v>2.1939799999999998</v>
+      </c>
+      <c r="Q6">
+        <v>4.9219299999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B7" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="30" t="s">
         <v>6</v>
       </c>
       <c r="D7">
@@ -2410,12 +2479,28 @@
         <f t="shared" ref="F7:F40" si="0">E7/D7</f>
         <v>9.4771030545525523</v>
       </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
+      <c r="I7">
+        <v>0.61763500000000005</v>
+      </c>
+      <c r="J7">
+        <v>0.71665500000000004</v>
+      </c>
+      <c r="K7">
+        <f t="shared" ref="K7:K40" si="1">J7/I7</f>
+        <v>1.160321225319161</v>
+      </c>
+      <c r="N7">
+        <v>2.2383899999999999</v>
+      </c>
+      <c r="Q7">
+        <v>4.9653299999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B8" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="31" t="s">
         <v>7</v>
       </c>
       <c r="D8">
@@ -2428,12 +2513,28 @@
         <f t="shared" si="0"/>
         <v>12.426179905121034</v>
       </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
+      <c r="I8">
+        <v>0.54384399999999999</v>
+      </c>
+      <c r="J8">
+        <v>0.80828599999999995</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="1"/>
+        <v>1.4862460558542523</v>
+      </c>
+      <c r="N8">
+        <v>2.3092999999999999</v>
+      </c>
+      <c r="Q8">
+        <v>5.0974500000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B9" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="32" t="s">
         <v>8</v>
       </c>
       <c r="D9">
@@ -2446,12 +2547,28 @@
         <f t="shared" si="0"/>
         <v>10.193750844002597</v>
       </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
+      <c r="I9">
+        <v>0.56194200000000005</v>
+      </c>
+      <c r="J9">
+        <v>0.77893000000000001</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="1"/>
+        <v>1.386139494823309</v>
+      </c>
+      <c r="N9">
+        <v>2.3016000000000001</v>
+      </c>
+      <c r="Q9">
+        <v>5.1799099999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B10" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="33" t="s">
         <v>9</v>
       </c>
       <c r="D10">
@@ -2464,12 +2581,28 @@
         <f t="shared" si="0"/>
         <v>7.4898606261610432</v>
       </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
+      <c r="I10">
+        <v>0.64870899999999998</v>
+      </c>
+      <c r="J10">
+        <v>0.71150899999999995</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="1"/>
+        <v>1.0968076595206788</v>
+      </c>
+      <c r="N10">
+        <v>2.3037899999999998</v>
+      </c>
+      <c r="Q10">
+        <v>5.2055999999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B11" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="29" t="s">
         <v>5</v>
       </c>
       <c r="D11">
@@ -2482,12 +2615,28 @@
         <f t="shared" si="0"/>
         <v>9.4487172623827451</v>
       </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
+      <c r="I11">
+        <v>0.64009199999999999</v>
+      </c>
+      <c r="J11">
+        <v>0.72269300000000003</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="1"/>
+        <v>1.1290455122076202</v>
+      </c>
+      <c r="N11">
+        <v>2.2228699999999999</v>
+      </c>
+      <c r="Q11">
+        <v>4.8518699999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B12" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="30" t="s">
         <v>6</v>
       </c>
       <c r="D12">
@@ -2500,12 +2649,28 @@
         <f t="shared" si="0"/>
         <v>10.810227993021023</v>
       </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
+      <c r="I12">
+        <v>0.62285500000000005</v>
+      </c>
+      <c r="J12">
+        <v>0.75607500000000005</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="1"/>
+        <v>1.2138860569474437</v>
+      </c>
+      <c r="N12">
+        <v>2.2550500000000002</v>
+      </c>
+      <c r="Q12">
+        <v>4.8645699999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B13" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="31" t="s">
         <v>7</v>
       </c>
       <c r="D13">
@@ -2518,12 +2683,28 @@
         <f t="shared" si="0"/>
         <v>14.549212199080335</v>
       </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
+      <c r="I13">
+        <v>0.55214399999999997</v>
+      </c>
+      <c r="J13">
+        <v>0.82074100000000005</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="1"/>
+        <v>1.4864618650207193</v>
+      </c>
+      <c r="N13">
+        <v>2.2866200000000001</v>
+      </c>
+      <c r="Q13">
+        <v>4.8790699999999996</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B14" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="32" t="s">
         <v>8</v>
       </c>
       <c r="D14">
@@ -2536,12 +2717,28 @@
         <f t="shared" si="0"/>
         <v>10.97435427254152</v>
       </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
+      <c r="I14">
+        <v>0.59609699999999999</v>
+      </c>
+      <c r="J14">
+        <v>0.78390000000000004</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="1"/>
+        <v>1.3150544290610422</v>
+      </c>
+      <c r="N14">
+        <v>2.3161900000000002</v>
+      </c>
+      <c r="Q14">
+        <v>5.0601099999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B15" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="33" t="s">
         <v>9</v>
       </c>
       <c r="D15">
@@ -2554,12 +2751,28 @@
         <f t="shared" si="0"/>
         <v>7.8958795857091157</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
+      <c r="I15">
+        <v>0.695295</v>
+      </c>
+      <c r="J15">
+        <v>0.71404800000000002</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="1"/>
+        <v>1.0269712855694346</v>
+      </c>
+      <c r="N15">
+        <v>2.3186200000000001</v>
+      </c>
+      <c r="Q15">
+        <v>5.1116799999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B16" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="29" t="s">
         <v>5</v>
       </c>
       <c r="D16">
@@ -2572,12 +2785,28 @@
         <f t="shared" si="0"/>
         <v>9.8874088169996828</v>
       </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
+      <c r="I16">
+        <v>0.50129500000000005</v>
+      </c>
+      <c r="J16">
+        <v>0.80508999999999997</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="1"/>
+        <v>1.6060204071454929</v>
+      </c>
+      <c r="N16">
+        <v>2.2135500000000001</v>
+      </c>
+      <c r="Q16">
+        <v>5.0569899999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B17" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="30" t="s">
         <v>6</v>
       </c>
       <c r="D17">
@@ -2590,12 +2819,28 @@
         <f t="shared" si="0"/>
         <v>10.752487562189057</v>
       </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
+      <c r="I17">
+        <v>0.52058700000000002</v>
+      </c>
+      <c r="J17">
+        <v>0.81447999999999998</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="1"/>
+        <v>1.5645415655788562</v>
+      </c>
+      <c r="N17">
+        <v>2.2620900000000002</v>
+      </c>
+      <c r="Q17">
+        <v>5.1066900000000004</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B18" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="31" t="s">
         <v>7</v>
       </c>
       <c r="D18">
@@ -2608,12 +2853,28 @@
         <f t="shared" si="0"/>
         <v>14.6828007518797</v>
       </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
+      <c r="I18">
+        <v>0.45558300000000002</v>
+      </c>
+      <c r="J18">
+        <v>0.89716099999999999</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="1"/>
+        <v>1.969259169020793</v>
+      </c>
+      <c r="N18">
+        <v>2.3234699999999999</v>
+      </c>
+      <c r="Q18">
+        <v>5.2081499999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B19" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="32" t="s">
         <v>8</v>
       </c>
       <c r="D19">
@@ -2626,12 +2887,28 @@
         <f t="shared" si="0"/>
         <v>11.828780116207861</v>
       </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
+      <c r="I19">
+        <v>0.46076899999999998</v>
+      </c>
+      <c r="J19">
+        <v>0.87839599999999995</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="1"/>
+        <v>1.90636956913334</v>
+      </c>
+      <c r="N19">
+        <v>2.31751</v>
+      </c>
+      <c r="Q19">
+        <v>5.3109999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B20" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="33" t="s">
         <v>9</v>
       </c>
       <c r="D20">
@@ -2644,12 +2921,28 @@
         <f t="shared" si="0"/>
         <v>8.5207382612840128</v>
       </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
+      <c r="I20">
+        <v>0.53098000000000001</v>
+      </c>
+      <c r="J20">
+        <v>0.827901</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="1"/>
+        <v>1.5591943199367209</v>
+      </c>
+      <c r="N20">
+        <v>2.3353600000000001</v>
+      </c>
+      <c r="Q20">
+        <v>5.38497</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B21" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="29" t="s">
         <v>5</v>
       </c>
       <c r="D21">
@@ -2662,12 +2955,28 @@
         <f t="shared" si="0"/>
         <v>10.37737519831753</v>
       </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
+      <c r="I21">
+        <v>0.53284699999999996</v>
+      </c>
+      <c r="J21">
+        <v>0.69206599999999996</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="1"/>
+        <v>1.2988081006367682</v>
+      </c>
+      <c r="N21">
+        <v>2.0272700000000001</v>
+      </c>
+      <c r="Q21">
+        <v>4.4920499999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B22" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="30" t="s">
         <v>6</v>
       </c>
       <c r="D22">
@@ -2680,12 +2989,28 @@
         <f t="shared" si="0"/>
         <v>11.527461531794868</v>
       </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
+      <c r="I22">
+        <v>0.54144499999999995</v>
+      </c>
+      <c r="J22">
+        <v>0.70456700000000005</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="1"/>
+        <v>1.3012715972998183</v>
+      </c>
+      <c r="N22">
+        <v>2.0664600000000002</v>
+      </c>
+      <c r="Q22">
+        <v>4.5264300000000004</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B23" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="31" t="s">
         <v>7</v>
       </c>
       <c r="D23">
@@ -2698,12 +3023,28 @@
         <f t="shared" si="0"/>
         <v>14.844168362429045</v>
       </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B24" t="s">
+      <c r="I23">
+        <v>0.47853299999999999</v>
+      </c>
+      <c r="J23">
+        <v>0.78290000000000004</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="1"/>
+        <v>1.6360418194774446</v>
+      </c>
+      <c r="N23">
+        <v>2.1239699999999999</v>
+      </c>
+      <c r="Q23">
+        <v>4.6309100000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B24" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="32" t="s">
         <v>8</v>
       </c>
       <c r="D24">
@@ -2716,12 +3057,28 @@
         <f t="shared" si="0"/>
         <v>12.166232830738503</v>
       </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
+      <c r="I24">
+        <v>0.49174099999999998</v>
+      </c>
+      <c r="J24">
+        <v>0.76219800000000004</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="1"/>
+        <v>1.5499988815250305</v>
+      </c>
+      <c r="N24">
+        <v>2.12357</v>
+      </c>
+      <c r="Q24">
+        <v>4.7167599999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B25" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="33" t="s">
         <v>9</v>
       </c>
       <c r="D25">
@@ -2734,12 +3091,28 @@
         <f t="shared" si="0"/>
         <v>8.6144671531109012</v>
       </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
+      <c r="I25">
+        <v>0.57181499999999996</v>
+      </c>
+      <c r="J25">
+        <v>0.70208300000000001</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="1"/>
+        <v>1.227814940146726</v>
+      </c>
+      <c r="N25">
+        <v>2.1311499999999999</v>
+      </c>
+      <c r="Q25">
+        <v>4.7605300000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B26" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="29" t="s">
         <v>5</v>
       </c>
       <c r="D26">
@@ -2752,12 +3125,28 @@
         <f t="shared" si="0"/>
         <v>10.76258898279236</v>
       </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
+      <c r="I26">
+        <v>0.71949099999999999</v>
+      </c>
+      <c r="J26">
+        <v>0.98144399999999998</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="1"/>
+        <v>1.3640809961486662</v>
+      </c>
+      <c r="N26">
+        <v>2.9456099999999998</v>
+      </c>
+      <c r="Q26">
+        <v>6.2612500000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B27" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="30" t="s">
         <v>6</v>
       </c>
       <c r="D27">
@@ -2770,12 +3159,28 @@
         <f t="shared" si="0"/>
         <v>12.326994615124477</v>
       </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
+      <c r="I27">
+        <v>0.65964</v>
+      </c>
+      <c r="J27">
+        <v>1.0618000000000001</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="1"/>
+        <v>1.6096658783578923</v>
+      </c>
+      <c r="N27">
+        <v>2.9668299999999999</v>
+      </c>
+      <c r="Q27">
+        <v>6.2421300000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B28" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="31" t="s">
         <v>7</v>
       </c>
       <c r="D28">
@@ -2788,12 +3193,28 @@
         <f t="shared" si="0"/>
         <v>15.705189719117151</v>
       </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
+      <c r="I28">
+        <v>0.57617099999999999</v>
+      </c>
+      <c r="J28">
+        <v>1.13896</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="1"/>
+        <v>1.9767742562537858</v>
+      </c>
+      <c r="N28">
+        <v>2.9452400000000001</v>
+      </c>
+      <c r="Q28">
+        <v>6.1063200000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B29" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="32" t="s">
         <v>8</v>
       </c>
       <c r="D29">
@@ -2806,12 +3227,28 @@
         <f t="shared" si="0"/>
         <v>11.597747659906396</v>
       </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
+      <c r="I29">
+        <v>0.68382900000000002</v>
+      </c>
+      <c r="J29">
+        <v>1.0379100000000001</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="1"/>
+        <v>1.5177917286339129</v>
+      </c>
+      <c r="N29">
+        <v>3.0378400000000001</v>
+      </c>
+      <c r="Q29">
+        <v>6.4434800000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B30" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="33" t="s">
         <v>9</v>
       </c>
       <c r="D30">
@@ -2824,12 +3261,28 @@
         <f t="shared" si="0"/>
         <v>9.1611307169137266</v>
       </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B31" t="s">
+      <c r="I30">
+        <v>0.81873700000000005</v>
+      </c>
+      <c r="J30">
+        <v>0.92295099999999997</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="1"/>
+        <v>1.1272862958434759</v>
+      </c>
+      <c r="N30">
+        <v>3.05694</v>
+      </c>
+      <c r="Q30">
+        <v>6.5531199999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B31" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="29" t="s">
         <v>5</v>
       </c>
       <c r="D31">
@@ -2842,12 +3295,22 @@
         <f t="shared" si="0"/>
         <v>8.9182201794876867</v>
       </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
+      <c r="I31">
+        <v>0.65654800000000002</v>
+      </c>
+      <c r="J31">
+        <v>0.84448500000000004</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="1"/>
+        <v>1.2862502056209142</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B32" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="30" t="s">
         <v>6</v>
       </c>
       <c r="D32">
@@ -2860,12 +3323,22 @@
         <f t="shared" si="0"/>
         <v>9.7572032150075465</v>
       </c>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
+      <c r="I32">
+        <v>0.66765600000000003</v>
+      </c>
+      <c r="J32">
+        <v>0.85654600000000003</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="1"/>
+        <v>1.2829151539115953</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B33" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="31" t="s">
         <v>7</v>
       </c>
       <c r="D33">
@@ -2878,12 +3351,22 @@
         <f t="shared" si="0"/>
         <v>13.895690447193555</v>
       </c>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B34" t="s">
+      <c r="I33">
+        <v>0.57942300000000002</v>
+      </c>
+      <c r="J33">
+        <v>0.94432400000000005</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="1"/>
+        <v>1.6297661639251462</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B34" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="32" t="s">
         <v>8</v>
       </c>
       <c r="D34">
@@ -2896,12 +3379,22 @@
         <f t="shared" si="0"/>
         <v>10.490300174751699</v>
       </c>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
+      <c r="I34">
+        <v>0.60229999999999995</v>
+      </c>
+      <c r="J34">
+        <v>0.92144999999999999</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="1"/>
+        <v>1.5298854391499255</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B35" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="33" t="s">
         <v>9</v>
       </c>
       <c r="D35">
@@ -2914,12 +3407,22 @@
         <f t="shared" si="0"/>
         <v>7.8074057070958256</v>
       </c>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
+      <c r="I35">
+        <v>0.68734700000000004</v>
+      </c>
+      <c r="J35">
+        <v>0.85840700000000003</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="1"/>
+        <v>1.2488699303263127</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B36" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="29" t="s">
         <v>5</v>
       </c>
       <c r="D36">
@@ -2932,12 +3435,22 @@
         <f t="shared" si="0"/>
         <v>8.8719844135006589</v>
       </c>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
+      <c r="I36">
+        <v>0.52019400000000005</v>
+      </c>
+      <c r="J36">
+        <v>0.87288699999999997</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="1"/>
+        <v>1.6780028220240908</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B37" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="30" t="s">
         <v>6</v>
       </c>
       <c r="D37">
@@ -2950,12 +3463,22 @@
         <f t="shared" si="0"/>
         <v>9.3734907510313796</v>
       </c>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
+      <c r="I37">
+        <v>0.54687399999999997</v>
+      </c>
+      <c r="J37">
+        <v>0.88549</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="1"/>
+        <v>1.6191846750805488</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B38" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="31" t="s">
         <v>7</v>
       </c>
       <c r="D38">
@@ -2968,12 +3491,22 @@
         <f t="shared" si="0"/>
         <v>13.917613823007686</v>
       </c>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
+      <c r="I38">
+        <v>0.47505500000000001</v>
+      </c>
+      <c r="J38">
+        <v>0.98697000000000001</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="1"/>
+        <v>2.0775910157771205</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B39" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="32" t="s">
         <v>8</v>
       </c>
       <c r="D39">
@@ -2986,12 +3519,22 @@
         <f t="shared" si="0"/>
         <v>10.812482503965768</v>
       </c>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
+      <c r="I39">
+        <v>0.47528300000000001</v>
+      </c>
+      <c r="J39">
+        <v>0.94490300000000005</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="1"/>
+        <v>1.9880849935722507</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B40" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="33" t="s">
         <v>9</v>
       </c>
       <c r="D40">
@@ -3003,6 +3546,26 @@
       <c r="F40">
         <f t="shared" si="0"/>
         <v>7.6714044598770661</v>
+      </c>
+      <c r="I40">
+        <v>0.544049</v>
+      </c>
+      <c r="J40">
+        <v>0.88444299999999998</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="1"/>
+        <v>1.6256679085891159</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="F41">
+        <f>AVERAGE(F6:F40)</f>
+        <v>10.749588389656193</v>
+      </c>
+      <c r="K41">
+        <f>AVERAGE(K6:K40)</f>
+        <v>1.4752314228410717</v>
       </c>
     </row>
   </sheetData>
